--- a/reports/exploring_ma_200.xlsx
+++ b/reports/exploring_ma_200.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dalva\src\project-hail-mary\reports\"/>
@@ -172,7 +172,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -240,8 +240,8 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
